--- a/v3/OG0005/OG0005_ReadingQuiz.xlsx
+++ b/v3/OG0005/OG0005_ReadingQuiz.xlsx
@@ -3179,7 +3179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>["outside.", "back", "ran", "and", "box", "the", "up", "picked", "He"]</t>
+          <t>["outside.", "back", "ran", "and", "the box", "up", "picked", "He"]</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>["He", "picked", "up", "the", "box", "and", "ran", "back", "outside."]</t>
+          <t>["He", "picked", "up", "the box", "and", "ran", "back", "outside."]</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr"/>
@@ -3535,7 +3535,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>the</t>
+          <t>the box</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
@@ -3561,7 +3561,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>and</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
@@ -3587,7 +3587,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>and</t>
+          <t>ran</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
@@ -3613,7 +3613,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>ran</t>
+          <t>back</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
@@ -3639,11 +3639,11 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>outside.</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
@@ -3663,90 +3663,64 @@
       <c r="H18" s="3" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>outside.</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>exact_position</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Actor/action/result word order.</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>SECTION D</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Diagnostics</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>SECTION D</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Diagnostics</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-      <c r="H20" s="4" t="inlineStr"/>
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Code</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>Threshold</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>attempt_sentence_gap</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B21" s="3" t="n">
         <v>70</v>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>인물이 문제를 해결하려고 한 행동 문장을 순서대로 구성하는 연습이 필요합니다.</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
